--- a/tests/fixtures/ratio.xlsx
+++ b/tests/fixtures/ratio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\MyPy\Packages\fltk\tests\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A37EBE1-DC06-4CB2-AD25-D81235B58994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1F438B-E145-4C60-A33D-F1455AC1D5D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{55D8B766-AA58-4EC0-B6FD-8EEF6CA6A6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{55D8B766-AA58-4EC0-B6FD-8EEF6CA6A6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="calc" sheetId="7" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="29">
   <si>
     <t>DirectLabor</t>
   </si>
@@ -140,9 +140,6 @@
   </si>
   <si>
     <t>den</t>
-  </si>
-  <si>
-    <t>pos</t>
   </si>
 </sst>
 </file>
@@ -191,7 +188,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -218,12 +215,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59996337778862885"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -237,12 +228,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59996337778862885"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -275,20 +260,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -650,23 +632,23 @@
       <c r="C2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="6" t="s">
         <v>7</v>
       </c>
       <c r="G2">
         <f>H2 / I2</f>
         <v>0.13043478260869565</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="7">
         <v>150</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="7">
         <v>1150</v>
       </c>
     </row>
@@ -680,13 +662,13 @@
       <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G3">
@@ -697,7 +679,7 @@
         <f>H2</f>
         <v>150</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="7">
         <v>1000</v>
       </c>
     </row>
@@ -711,13 +693,13 @@
       <c r="C4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="8" t="s">
+      <c r="E4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="G4">
@@ -760,7 +742,7 @@
         <f>I3</f>
         <v>1000</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="7">
         <v>175</v>
       </c>
     </row>
@@ -791,7 +773,7 @@
         <f>I3</f>
         <v>1000</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="7">
         <v>300</v>
       </c>
     </row>
@@ -837,23 +819,23 @@
       <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="6" t="s">
         <v>7</v>
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
         <v>0.12</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="7">
         <v>120</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="7">
         <v>1000</v>
       </c>
     </row>
@@ -867,13 +849,13 @@
       <c r="C9" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G9">
@@ -884,7 +866,7 @@
         <f>H8</f>
         <v>120</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="7">
         <v>1100</v>
       </c>
     </row>
@@ -898,13 +880,13 @@
       <c r="C10" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="8" t="s">
+      <c r="E10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>7</v>
       </c>
       <c r="G10">
@@ -947,7 +929,7 @@
         <f>I9</f>
         <v>1100</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="7">
         <v>160</v>
       </c>
     </row>
@@ -978,7 +960,7 @@
         <f>I9</f>
         <v>1100</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="7">
         <v>275</v>
       </c>
     </row>
@@ -1015,7 +997,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -1024,28 +1006,28 @@
       <c r="C14" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="6" t="s">
         <v>7</v>
       </c>
       <c r="G14">
         <f>H14 / I14</f>
         <v>0.13043478260869565</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="7">
         <v>150</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="7">
         <v>1150</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -1054,13 +1036,13 @@
       <c r="C15" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G15" t="e">
@@ -1071,10 +1053,10 @@
         <f>H14</f>
         <v>150</v>
       </c>
-      <c r="I15" s="9"/>
+      <c r="I15" s="7"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -1083,13 +1065,13 @@
       <c r="C16" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" s="8" t="s">
+      <c r="E16" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>7</v>
       </c>
       <c r="G16">
@@ -1106,7 +1088,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -1132,13 +1114,13 @@
         <f>I15</f>
         <v>0</v>
       </c>
-      <c r="I17" s="9" t="e">
+      <c r="I17" s="7" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -1164,12 +1146,12 @@
         <f>I15</f>
         <v>0</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -1201,7 +1183,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -1210,28 +1192,28 @@
       <c r="C20" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="6" t="s">
         <v>7</v>
       </c>
       <c r="G20">
         <f t="shared" si="1"/>
         <v>9.9999999999999991E-11</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="7">
         <v>9.9999999999999995E-8</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="7">
         <v>1000</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -1240,13 +1222,13 @@
       <c r="C21" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G21">
@@ -1257,12 +1239,12 @@
         <f>H20</f>
         <v>9.9999999999999995E-8</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="7">
         <v>9.9999999999999995E-8</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -1271,13 +1253,13 @@
       <c r="C22" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" s="8" t="s">
+      <c r="E22" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>7</v>
       </c>
       <c r="G22">
@@ -1294,7 +1276,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -1320,12 +1302,12 @@
         <f>I21</f>
         <v>9.9999999999999995E-8</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="7">
         <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -1351,10 +1333,10 @@
         <f>I21</f>
         <v>9.9999999999999995E-8</v>
       </c>
-      <c r="I24" s="9"/>
+      <c r="I24" s="7"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -1392,1033 +1374,388 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7617727C-825D-45EB-8828-1D5514C26C65}">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="30.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="30.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="8" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F2">
+      <c r="E2">
         <f>calc!H2</f>
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <f>calc!H3</f>
-        <v>150</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3">
         <f>calc!H4</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <f>calc!H5</f>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <f>calc!H6</f>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
         <v>4</v>
       </c>
-      <c r="F7">
+      <c r="E4">
         <f>calc!H7</f>
         <v>300</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="8" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F8">
+      <c r="E5">
         <f>calc!H8</f>
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <f>calc!H9</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6">
         <f>calc!H10</f>
         <v>1100</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
         <v>25</v>
       </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11">
-        <f>calc!H11</f>
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12">
-        <f>calc!H12</f>
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="D7" t="s">
         <v>4</v>
       </c>
-      <c r="F13">
+      <c r="E7">
         <f>calc!H13</f>
         <v>275</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="6" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="8" t="s">
+      <c r="B8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F14">
+      <c r="E8">
         <f>calc!H14</f>
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="6" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="8" t="s">
+      <c r="B9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9">
+        <f>calc!H16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <f>calc!H19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F15">
-        <f>calc!H15</f>
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16">
-        <f>calc!H16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17">
-        <f>calc!H17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18">
-        <f>calc!H18</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" t="s">
-        <v>4</v>
-      </c>
-      <c r="F19">
-        <f>calc!H19</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20">
+      <c r="E11">
         <f>calc!H20</f>
         <v>9.9999999999999995E-8</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="7" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F21">
-        <f>calc!H21</f>
-        <v>9.9999999999999995E-8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22">
+      <c r="B12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12">
         <f>calc!H22</f>
         <v>9.9999999999999995E-8</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="7" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="B13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
         <v>25</v>
       </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23">
-        <f>calc!H23</f>
-        <v>9.9999999999999995E-8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24">
-        <f>calc!H24</f>
-        <v>9.9999999999999995E-8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="D13" t="s">
         <v>4</v>
       </c>
-      <c r="F25">
+      <c r="E13">
         <f>calc!H25</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="8" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F26">
+      <c r="E14">
         <f>calc!I2</f>
         <v>1150</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27">
-        <f>calc!I3</f>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28">
-        <f>calc!I4</f>
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" t="s">
-        <v>0</v>
-      </c>
-      <c r="F29">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
+        <v>0</v>
+      </c>
+      <c r="E15">
         <f>calc!I5</f>
         <v>175</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" t="s">
-        <v>4</v>
-      </c>
-      <c r="F30">
-        <f>calc!I6</f>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" t="s">
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <f>calc!I7</f>
-        <v>175</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D32" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="8" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F32">
+      <c r="E16">
         <f>calc!I8</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33">
-        <f>calc!I9</f>
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D34" t="s">
-        <v>20</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34">
-        <f>calc!I10</f>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
         <v>25</v>
       </c>
-      <c r="E35" t="s">
-        <v>0</v>
-      </c>
-      <c r="F35">
+      <c r="D17" t="s">
+        <v>0</v>
+      </c>
+      <c r="E17">
         <f>calc!I11</f>
         <v>160</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D36" t="s">
-        <v>25</v>
-      </c>
-      <c r="E36" t="s">
-        <v>4</v>
-      </c>
-      <c r="F36">
-        <f>calc!I12</f>
-        <v>275</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D37" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37" t="s">
-        <v>0</v>
-      </c>
-      <c r="F37">
-        <f>calc!I13</f>
-        <v>160</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B38" s="6" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D38" t="s">
-        <v>20</v>
-      </c>
-      <c r="E38" s="8" t="s">
+      <c r="B18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F38">
+      <c r="E18">
         <f>calc!I14</f>
         <v>1150</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B39" s="6" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D39" t="s">
-        <v>20</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F39" s="4"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D40" t="s">
-        <v>20</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40">
-        <f>calc!I16</f>
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D41" t="s">
-        <v>20</v>
-      </c>
-      <c r="E41" t="s">
-        <v>0</v>
-      </c>
-      <c r="F41" t="e">
+      <c r="B19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" t="s">
+        <v>0</v>
+      </c>
+      <c r="E19" t="e">
         <f>calc!I17</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D42" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" t="s">
-        <v>4</v>
-      </c>
-      <c r="F42">
-        <f>calc!I18</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D43" t="s">
-        <v>20</v>
-      </c>
-      <c r="E43" t="s">
-        <v>0</v>
-      </c>
-      <c r="F43" t="e">
-        <f>calc!I19</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B44" s="7" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D44" t="s">
-        <v>20</v>
-      </c>
-      <c r="E44" s="8" t="s">
+      <c r="B20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F44">
+      <c r="E20">
         <f>calc!I20</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B45" s="7" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45" t="s">
-        <v>20</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F45">
-        <f>calc!I21</f>
-        <v>9.9999999999999995E-8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D46" t="s">
-        <v>20</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46">
-        <f>calc!I22</f>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="B21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" t="s">
         <v>25</v>
       </c>
-      <c r="E47" t="s">
-        <v>0</v>
-      </c>
-      <c r="F47">
+      <c r="D21" t="s">
+        <v>0</v>
+      </c>
+      <c r="E21">
         <f>calc!I23</f>
-        <v>160</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D48" t="s">
-        <v>25</v>
-      </c>
-      <c r="E48" t="s">
-        <v>4</v>
-      </c>
-      <c r="F48" s="9"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D49" t="s">
-        <v>25</v>
-      </c>
-      <c r="E49" t="s">
-        <v>0</v>
-      </c>
-      <c r="F49">
-        <f>calc!I25</f>
         <v>160</v>
       </c>
     </row>
@@ -2452,69 +1789,69 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>0</v>
+      <c r="A2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>0</v>
+      <c r="A3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C4" t="s">
-        <v>6</v>
+      <c r="C4" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/tests/fixtures/ratio.xlsx
+++ b/tests/fixtures/ratio.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\MyPy\Packages\fltk\tests\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1F438B-E145-4C60-A33D-F1455AC1D5D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4634275E-711D-4BF9-957D-8909CB3451EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{55D8B766-AA58-4EC0-B6FD-8EEF6CA6A6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{55D8B766-AA58-4EC0-B6FD-8EEF6CA6A6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="calc" sheetId="7" r:id="rId1"/>
     <sheet name="data1" sheetId="6" r:id="rId2"/>
     <sheet name="concepts_ratios" sheetId="5" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">data1!$A$1:$E$22</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -53,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="30">
   <si>
     <t>DirectLabor</t>
   </si>
@@ -140,13 +143,16 @@
   </si>
   <si>
     <t>den</t>
+  </si>
+  <si>
+    <t>inf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,13 +186,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -209,12 +208,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59996337778862885"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -228,6 +221,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -260,17 +259,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -586,14 +590,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A61EEF6B-52C6-492C-B13D-8396A5497842}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="6" width="30.7109375" customWidth="1"/>
     <col min="7" max="9" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
@@ -622,7 +626,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>19</v>
       </c>
@@ -645,14 +649,19 @@
         <f>H2 / I2</f>
         <v>0.13043478260869565</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2">
+        <f>data1!$E$3</f>
         <v>150</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2">
+        <f>data1!$E$6</f>
         <v>1150</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2">
+        <v>0.13043478260869559</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
@@ -676,14 +685,18 @@
         <v>0.15</v>
       </c>
       <c r="H3">
-        <f>H2</f>
+        <f>data1!$E$3</f>
         <v>150</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3">
+        <f>data1!$E$5</f>
         <v>1000</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -707,15 +720,18 @@
         <v>0.86956521739130432</v>
       </c>
       <c r="H4">
-        <f>I3</f>
+        <f>data1!$E$5</f>
         <v>1000</v>
       </c>
       <c r="I4">
-        <f>I2</f>
+        <f>data1!$E$6</f>
         <v>1150</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4">
+        <v>0.86956521739130432</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
@@ -739,14 +755,18 @@
         <v>5.7142857142857144</v>
       </c>
       <c r="H5">
-        <f>I3</f>
+        <f>data1!$E$5</f>
         <v>1000</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5">
+        <f>data1!$E$2</f>
         <v>175</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J5">
+        <v>5.7142857142857144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -770,14 +790,18 @@
         <v>3.3333333333333335</v>
       </c>
       <c r="H6">
-        <f>I3</f>
+        <f>data1!$E$5</f>
         <v>1000</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6">
+        <f>data1!$E$4</f>
         <v>300</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6">
+        <v>3.333333333333333</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
@@ -801,19 +825,22 @@
         <v>1.7142857142857142</v>
       </c>
       <c r="H7">
-        <f>I6</f>
+        <f>data1!$E$4</f>
         <v>300</v>
       </c>
       <c r="I7">
-        <f>I5</f>
+        <f>data1!$E$2</f>
         <v>175</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J7">
+        <v>1.714285714285714</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="7" t="s">
         <v>22</v>
       </c>
       <c r="C8" t="s">
@@ -832,18 +859,23 @@
         <f t="shared" si="0"/>
         <v>0.12</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8">
+        <f>data1!$E$7</f>
         <v>120</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8">
+        <f>data1!$E$9</f>
         <v>1000</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J8">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="7" t="s">
         <v>22</v>
       </c>
       <c r="C9" t="s">
@@ -863,18 +895,22 @@
         <v>0.10909090909090909</v>
       </c>
       <c r="H9">
-        <f>H8</f>
+        <f>data1!$E$7</f>
         <v>120</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9">
+        <f>data1!$E$8</f>
         <v>1100</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J9">
+        <v>0.1090909090909091</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="7" t="s">
         <v>22</v>
       </c>
       <c r="C10" t="s">
@@ -894,19 +930,22 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="H10">
-        <f>I9</f>
+        <f>data1!$E$8</f>
         <v>1100</v>
       </c>
       <c r="I10">
-        <f>I8</f>
+        <f>data1!$E$9</f>
         <v>1000</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J10">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="8" t="s">
         <v>22</v>
       </c>
       <c r="C11" t="s">
@@ -926,18 +965,22 @@
         <v>6.875</v>
       </c>
       <c r="H11">
-        <f>I9</f>
-        <v>1100</v>
-      </c>
-      <c r="I11" s="7">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <f>data1!$E$12</f>
+        <v>275</v>
+      </c>
+      <c r="I11">
+        <f>data1!$E$10</f>
+        <v>40</v>
+      </c>
+      <c r="J11">
+        <v>6.875</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="8" t="s">
         <v>22</v>
       </c>
       <c r="C12" t="s">
@@ -954,21 +997,25 @@
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="H12">
-        <f>I9</f>
-        <v>1100</v>
-      </c>
-      <c r="I12" s="7">
+        <f>data1!$E$12</f>
         <v>275</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I12">
+        <f>data1!$E$11</f>
+        <v>50</v>
+      </c>
+      <c r="J12">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="8" t="s">
         <v>22</v>
       </c>
       <c r="C13" t="s">
@@ -985,18 +1032,21 @@
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>1.71875</v>
+        <v>1.25</v>
       </c>
       <c r="H13">
-        <f>I12</f>
-        <v>275</v>
+        <f>data1!$E$11</f>
+        <v>50</v>
       </c>
       <c r="I13">
-        <f>I11</f>
-        <v>160</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <f>data1!$E$10</f>
+        <v>40</v>
+      </c>
+      <c r="J13">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>23</v>
       </c>
@@ -1019,14 +1069,19 @@
         <f>H14 / I14</f>
         <v>0.13043478260869565</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14">
+        <f>data1!$E$14</f>
         <v>150</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14">
+        <f>data1!$E$17</f>
         <v>1150</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J14">
+        <v>0.13043478260869559</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
@@ -1050,12 +1105,18 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H15">
-        <f>H14</f>
+        <f>data1!$E$14</f>
         <v>150</v>
       </c>
-      <c r="I15" s="7"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I15">
+        <f>data1!$E$16</f>
+        <v>0</v>
+      </c>
+      <c r="J15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>23</v>
       </c>
@@ -1079,15 +1140,18 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <f>I15</f>
+        <f>data1!$E$16</f>
         <v>0</v>
       </c>
       <c r="I16">
-        <f>I14</f>
+        <f>data1!$E$17</f>
         <v>1150</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>23</v>
       </c>
@@ -1111,15 +1175,15 @@
         <v>#N/A</v>
       </c>
       <c r="H17">
-        <f>I15</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="7" t="e">
-        <f>NA()</f>
+        <f>data1!$E$16</f>
+        <v>0</v>
+      </c>
+      <c r="I17" t="e">
+        <f>data1!$E$13</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>23</v>
       </c>
@@ -1143,14 +1207,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H18">
-        <f>I15</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <f>data1!$E$16</f>
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <f>data1!$E$15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>23</v>
       </c>
@@ -1174,15 +1239,15 @@
         <v>#N/A</v>
       </c>
       <c r="H19">
-        <f>I18</f>
+        <f>data1!$E$15</f>
         <v>0</v>
       </c>
       <c r="I19" t="e">
-        <f>I17</f>
+        <f>data1!$E$13</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>24</v>
       </c>
@@ -1205,14 +1270,19 @@
         <f t="shared" si="1"/>
         <v>9.9999999999999991E-11</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20">
+        <f>data1!$E$18</f>
         <v>9.9999999999999995E-8</v>
       </c>
-      <c r="I20" s="7">
+      <c r="I20">
+        <f>data1!$E$20</f>
         <v>1000</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J20">
+        <v>9.9999999999999991E-11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>24</v>
       </c>
@@ -1236,14 +1306,18 @@
         <v>1</v>
       </c>
       <c r="H21">
-        <f>H20</f>
+        <f>data1!$E$18</f>
         <v>9.9999999999999995E-8</v>
       </c>
-      <c r="I21" s="7">
+      <c r="I21">
+        <f>data1!$E$19</f>
         <v>9.9999999999999995E-8</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>24</v>
       </c>
@@ -1267,15 +1341,18 @@
         <v>9.9999999999999991E-11</v>
       </c>
       <c r="H22">
-        <f>I21</f>
+        <f>data1!$E$19</f>
         <v>9.9999999999999995E-8</v>
       </c>
       <c r="I22">
-        <f>I20</f>
+        <f>data1!$E$20</f>
         <v>1000</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J22">
+        <v>9.9999999999999995E-8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>24</v>
       </c>
@@ -1296,17 +1373,14 @@
       </c>
       <c r="G23">
         <f t="shared" si="1"/>
-        <v>6.2500000000000001E-10</v>
-      </c>
-      <c r="H23">
-        <f>I21</f>
-        <v>9.9999999999999995E-8</v>
-      </c>
-      <c r="I23" s="7">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <f>data1!$E$21</f>
         <v>160</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>24</v>
       </c>
@@ -1329,13 +1403,12 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H24">
-        <f>I21</f>
-        <v>9.9999999999999995E-8</v>
-      </c>
-      <c r="I24" s="7"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I24">
+        <f>data1!$E$22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>24</v>
       </c>
@@ -1359,12 +1432,15 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <f>I24</f>
+        <f>data1!$E$22</f>
         <v>0</v>
       </c>
       <c r="I25">
-        <f>I23</f>
+        <f>data1!$E$21</f>
         <v>160</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1374,7 +1450,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7617727C-825D-45EB-8828-1D5514C26C65}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
@@ -1409,12 +1485,11 @@
       <c r="C2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>1</v>
+      <c r="D2" t="s">
+        <v>0</v>
       </c>
       <c r="E2">
-        <f>calc!H2</f>
-        <v>150</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1427,12 +1502,11 @@
       <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>6</v>
+      <c r="D3" t="s">
+        <v>1</v>
       </c>
       <c r="E3">
-        <f>calc!H4</f>
-        <v>1000</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1449,7 +1523,6 @@
         <v>4</v>
       </c>
       <c r="E4">
-        <f>calc!H7</f>
         <v>300</v>
       </c>
     </row>
@@ -1458,17 +1531,16 @@
         <v>19</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>1</v>
+      <c r="D5" t="s">
+        <v>6</v>
       </c>
       <c r="E5">
-        <f>calc!H8</f>
-        <v>120</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1476,251 +1548,237 @@
         <v>19</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>6</v>
+      <c r="D6" t="s">
+        <v>7</v>
       </c>
       <c r="E6">
-        <f>calc!H10</f>
-        <v>1100</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="7" t="s">
         <v>22</v>
       </c>
       <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
         <v>25</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D10" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
         <v>4</v>
       </c>
-      <c r="E7">
-        <f>calc!H13</f>
+      <c r="E11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12">
         <v>275</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="6" t="s">
+      <c r="B13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E13" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" t="s">
         <v>1</v>
       </c>
-      <c r="E8">
-        <f>calc!H14</f>
+      <c r="E14">
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9">
-        <f>calc!H16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="B15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10">
-        <f>calc!H19</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="6" t="s">
+      <c r="B18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" t="s">
         <v>1</v>
       </c>
-      <c r="E11">
-        <f>calc!H20</f>
+      <c r="E18">
         <v>9.9999999999999995E-8</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12">
-        <f>calc!H22</f>
+      <c r="B19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19">
         <v>9.9999999999999995E-8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13">
-        <f>calc!H25</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14">
-        <f>calc!I2</f>
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" t="s">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <f>calc!I5</f>
-        <v>175</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16">
-        <f>calc!I8</f>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" t="s">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <f>calc!I11</f>
-        <v>160</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18">
-        <f>calc!I14</f>
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" t="s">
-        <v>0</v>
-      </c>
-      <c r="E19" t="e">
-        <f>calc!I17</f>
-        <v>#N/A</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1733,11 +1791,10 @@
       <c r="C20" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" t="s">
         <v>7</v>
       </c>
       <c r="E20">
-        <f>calc!I20</f>
         <v>1000</v>
       </c>
     </row>
@@ -1755,12 +1812,35 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <f>calc!I23</f>
         <v>160</v>
       </c>
     </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E22">
+    <sortCondition ref="A2:A22"/>
+    <sortCondition ref="B2:B22"/>
+    <sortCondition ref="C2:C22"/>
+    <sortCondition ref="D2:D22"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/tests/fixtures/ratio.xlsx
+++ b/tests/fixtures/ratio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\MyPy\Packages\fltk\tests\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4634275E-711D-4BF9-957D-8909CB3451EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8654C0C-291F-463D-B390-C2455CB11F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{55D8B766-AA58-4EC0-B6FD-8EEF6CA6A6EF}"/>
+    <workbookView xWindow="4455" yWindow="3465" windowWidth="28800" windowHeight="11295" activeTab="1" xr2:uid="{55D8B766-AA58-4EC0-B6FD-8EEF6CA6A6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="calc" sheetId="7" r:id="rId1"/>
@@ -1463,10 +1463,10 @@
         <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>15</v>

--- a/tests/fixtures/ratio.xlsx
+++ b/tests/fixtures/ratio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\MyPy\Packages\fltk\tests\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8654C0C-291F-463D-B390-C2455CB11F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0B42FC-38B3-4A98-9004-55EE5D4CD050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4455" yWindow="3465" windowWidth="28800" windowHeight="11295" activeTab="1" xr2:uid="{55D8B766-AA58-4EC0-B6FD-8EEF6CA6A6EF}"/>
+    <workbookView xWindow="8985" yWindow="4185" windowWidth="28800" windowHeight="11295" xr2:uid="{55D8B766-AA58-4EC0-B6FD-8EEF6CA6A6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="calc" sheetId="7" r:id="rId1"/>
